--- a/65_Threshold_OUTPUT/direct_P0A7C2_Escherichia_coli.xlsx
+++ b/65_Threshold_OUTPUT/direct_P0A7C2_Escherichia_coli.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TTTTTTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TTTTTT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TTTTTT</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.03978408636545382</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TTTTTTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TTTTT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.1689324270291883</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>TTTTTTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>TTTT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>TTTT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.5373850459816074</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TTTTTTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;T&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9854058376649341</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>TGTTTTTTTGT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>TGT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TTTTT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9854058376649341</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>TTTTTTT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TTT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -651,15 +721,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>ACTGTTTTTTTGTAC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;TGTTTTTTTGT&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -680,15 +760,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>GTTTTTTTGTACAGT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TTTTTTGTACA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
@@ -709,15 +799,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>GTACAGT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;ACA&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9998000799680128</v>
       </c>
     </row>
